--- a/九龙-旺角-映居/映居_销控明细表.xlsx
+++ b/九龙-旺角-映居/映居_销控明细表.xlsx
@@ -826,7 +826,7 @@
       </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="H4" s="5" t="n">
@@ -1198,7 +1198,7 @@
       </c>
       <c r="G10" s="3" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="H10" s="5" t="n">
@@ -1384,7 +1384,7 @@
       </c>
       <c r="G13" s="3" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="H13" s="5" t="n">
@@ -1508,7 +1508,7 @@
       </c>
       <c r="G15" s="3" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="H15" s="5" t="n">
@@ -1570,7 +1570,7 @@
       </c>
       <c r="G16" s="3" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="H16" s="5" t="n">
@@ -1632,7 +1632,7 @@
       </c>
       <c r="G17" s="3" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="H17" s="5" t="n">
@@ -1756,7 +1756,7 @@
       </c>
       <c r="G19" s="3" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="H19" s="5" t="n">
@@ -1880,7 +1880,7 @@
       </c>
       <c r="G21" s="3" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="H21" s="5" t="n">
@@ -1942,7 +1942,7 @@
       </c>
       <c r="G22" s="3" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="H22" s="5" t="n">
@@ -2066,7 +2066,7 @@
       </c>
       <c r="G24" s="3" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="H24" s="5" t="n">
@@ -2128,7 +2128,7 @@
       </c>
       <c r="G25" s="3" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="H25" s="5" t="n">
@@ -2252,7 +2252,7 @@
       </c>
       <c r="G27" s="3" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="H27" s="5" t="n">
@@ -2314,7 +2314,7 @@
       </c>
       <c r="G28" s="3" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="H28" s="5" t="n">
@@ -2376,7 +2376,7 @@
       </c>
       <c r="G29" s="3" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="H29" s="5" t="n">
@@ -2438,7 +2438,7 @@
       </c>
       <c r="G30" s="3" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="H30" s="5" t="n">
@@ -2500,7 +2500,7 @@
       </c>
       <c r="G31" s="3" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="H31" s="5" t="n">
@@ -2624,7 +2624,7 @@
       </c>
       <c r="G33" s="3" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="H33" s="5" t="n">
@@ -2686,7 +2686,7 @@
       </c>
       <c r="G34" s="3" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="H34" s="5" t="n">
@@ -2748,7 +2748,7 @@
       </c>
       <c r="G35" s="3" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="H35" s="5" t="n">
@@ -2810,7 +2810,7 @@
       </c>
       <c r="G36" s="3" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="H36" s="5" t="n">
@@ -2872,7 +2872,7 @@
       </c>
       <c r="G37" s="3" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="H37" s="5" t="n">
@@ -2996,7 +2996,7 @@
       </c>
       <c r="G39" s="3" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="H39" s="5" t="n">
@@ -3058,7 +3058,7 @@
       </c>
       <c r="G40" s="3" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="H40" s="5" t="n">
@@ -3120,7 +3120,7 @@
       </c>
       <c r="G41" s="3" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="H41" s="5" t="n">
@@ -3182,7 +3182,7 @@
       </c>
       <c r="G42" s="3" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="H42" s="5" t="n">
@@ -3244,7 +3244,7 @@
       </c>
       <c r="G43" s="3" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="H43" s="5" t="n">
@@ -3306,7 +3306,7 @@
       </c>
       <c r="G44" s="3" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="H44" s="5" t="n">
@@ -3368,7 +3368,7 @@
       </c>
       <c r="G45" s="3" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="H45" s="5" t="n">
@@ -3430,7 +3430,7 @@
       </c>
       <c r="G46" s="3" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="H46" s="5" t="n">
@@ -3492,7 +3492,7 @@
       </c>
       <c r="G47" s="3" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="H47" s="5" t="n">
@@ -3554,7 +3554,7 @@
       </c>
       <c r="G48" s="3" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="H48" s="5" t="n">
@@ -3616,7 +3616,7 @@
       </c>
       <c r="G49" s="3" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="H49" s="5" t="n">
@@ -3678,7 +3678,7 @@
       </c>
       <c r="G50" s="3" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="H50" s="5" t="n">
@@ -3740,7 +3740,7 @@
       </c>
       <c r="G51" s="3" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="H51" s="5" t="n">
@@ -3802,7 +3802,7 @@
       </c>
       <c r="G52" s="3" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="H52" s="5" t="n">
@@ -3864,7 +3864,7 @@
       </c>
       <c r="G53" s="3" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="H53" s="5" t="n">
@@ -3926,7 +3926,7 @@
       </c>
       <c r="G54" s="3" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="H54" s="5" t="n">
@@ -3988,7 +3988,7 @@
       </c>
       <c r="G55" s="3" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="H55" s="5" t="n">
@@ -4050,7 +4050,7 @@
       </c>
       <c r="G56" s="3" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="H56" s="5" t="n">
@@ -4112,7 +4112,7 @@
       </c>
       <c r="G57" s="3" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="H57" s="5" t="n">
@@ -4174,7 +4174,7 @@
       </c>
       <c r="G58" s="3" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="H58" s="5" t="n">
@@ -4236,7 +4236,7 @@
       </c>
       <c r="G59" s="3" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="H59" s="5" t="n">
@@ -4298,7 +4298,7 @@
       </c>
       <c r="G60" s="3" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="H60" s="5" t="n">
@@ -4360,7 +4360,7 @@
       </c>
       <c r="G61" s="3" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="H61" s="5" t="n">
@@ -4422,7 +4422,7 @@
       </c>
       <c r="G62" s="3" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="H62" s="5" t="n">
@@ -4484,7 +4484,7 @@
       </c>
       <c r="G63" s="3" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="H63" s="5" t="n">
@@ -4546,7 +4546,7 @@
       </c>
       <c r="G64" s="3" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="H64" s="5" t="n">
@@ -4608,7 +4608,7 @@
       </c>
       <c r="G65" s="3" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="H65" s="5" t="n">
@@ -4670,7 +4670,7 @@
       </c>
       <c r="G66" s="3" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="H66" s="5" t="n">
@@ -4732,7 +4732,7 @@
       </c>
       <c r="G67" s="3" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="H67" s="5" t="n">
@@ -4794,7 +4794,7 @@
       </c>
       <c r="G68" s="3" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="H68" s="5" t="n">
@@ -4856,7 +4856,7 @@
       </c>
       <c r="G69" s="3" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="H69" s="5" t="n">
@@ -4918,7 +4918,7 @@
       </c>
       <c r="G70" s="3" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="H70" s="5" t="n">
@@ -4980,7 +4980,7 @@
       </c>
       <c r="G71" s="3" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="H71" s="5" t="n">
@@ -5042,7 +5042,7 @@
       </c>
       <c r="G72" s="3" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="H72" s="5" t="n">
@@ -5104,7 +5104,7 @@
       </c>
       <c r="G73" s="3" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="H73" s="5" t="n">
@@ -5166,7 +5166,7 @@
       </c>
       <c r="G74" s="3" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="H74" s="5" t="n">
@@ -5228,7 +5228,7 @@
       </c>
       <c r="G75" s="3" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="H75" s="5" t="n">
@@ -5290,7 +5290,7 @@
       </c>
       <c r="G76" s="3" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="H76" s="5" t="n">
@@ -5352,7 +5352,7 @@
       </c>
       <c r="G77" s="3" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="H77" s="5" t="n">
@@ -5414,7 +5414,7 @@
       </c>
       <c r="G78" s="3" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="H78" s="5" t="n">
@@ -5476,7 +5476,7 @@
       </c>
       <c r="G79" s="3" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="H79" s="5" t="n">
@@ -5538,7 +5538,7 @@
       </c>
       <c r="G80" s="3" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="H80" s="5" t="n">
@@ -5600,7 +5600,7 @@
       </c>
       <c r="G81" s="3" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="H81" s="5" t="n">
@@ -5662,7 +5662,7 @@
       </c>
       <c r="G82" s="3" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="H82" s="5" t="n">
@@ -5724,7 +5724,7 @@
       </c>
       <c r="G83" s="3" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="H83" s="5" t="n">
@@ -5786,7 +5786,7 @@
       </c>
       <c r="G84" s="3" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="H84" s="5" t="n">
@@ -5848,7 +5848,7 @@
       </c>
       <c r="G85" s="3" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="H85" s="5" t="n">
@@ -5910,7 +5910,7 @@
       </c>
       <c r="G86" s="3" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="H86" s="5" t="n">
@@ -5972,7 +5972,7 @@
       </c>
       <c r="G87" s="3" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="H87" s="5" t="n">
@@ -6034,7 +6034,7 @@
       </c>
       <c r="G88" s="3" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="H88" s="5" t="n">
@@ -6096,7 +6096,7 @@
       </c>
       <c r="G89" s="3" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="H89" s="5" t="n">
@@ -6158,7 +6158,7 @@
       </c>
       <c r="G90" s="3" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="H90" s="5" t="n">
@@ -6220,7 +6220,7 @@
       </c>
       <c r="G91" s="3" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="H91" s="5" t="n">
@@ -6282,7 +6282,7 @@
       </c>
       <c r="G92" s="3" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="H92" s="5" t="n">
@@ -6344,7 +6344,7 @@
       </c>
       <c r="G93" s="3" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="H93" s="5" t="n">
@@ -6406,7 +6406,7 @@
       </c>
       <c r="G94" s="3" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="H94" s="5" t="n">
@@ -6468,7 +6468,7 @@
       </c>
       <c r="G95" s="3" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="H95" s="5" t="n">
@@ -6530,7 +6530,7 @@
       </c>
       <c r="G96" s="3" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="H96" s="5" t="n">
@@ -6592,7 +6592,7 @@
       </c>
       <c r="G97" s="3" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="H97" s="5" t="n">
@@ -6654,7 +6654,7 @@
       </c>
       <c r="G98" s="3" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="H98" s="5" t="n">
@@ -6716,7 +6716,7 @@
       </c>
       <c r="G99" s="3" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="H99" s="5" t="n">
@@ -6778,7 +6778,7 @@
       </c>
       <c r="G100" s="3" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="H100" s="5" t="n">
@@ -6840,7 +6840,7 @@
       </c>
       <c r="G101" s="3" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="H101" s="5" t="n">
@@ -6902,7 +6902,7 @@
       </c>
       <c r="G102" s="3" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="H102" s="5" t="n">
@@ -6964,7 +6964,7 @@
       </c>
       <c r="G103" s="3" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="H103" s="5" t="n">
@@ -7026,7 +7026,7 @@
       </c>
       <c r="G104" s="3" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="H104" s="5" t="n">
@@ -7088,7 +7088,7 @@
       </c>
       <c r="G105" s="3" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="H105" s="5" t="n">
@@ -7150,7 +7150,7 @@
       </c>
       <c r="G106" s="3" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="H106" s="5" t="n">
@@ -7212,7 +7212,7 @@
       </c>
       <c r="G107" s="3" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="H107" s="5" t="n">
@@ -7274,7 +7274,7 @@
       </c>
       <c r="G108" s="3" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="H108" s="5" t="n">
@@ -7336,7 +7336,7 @@
       </c>
       <c r="G109" s="3" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="H109" s="5" t="n">
@@ -7398,7 +7398,7 @@
       </c>
       <c r="G110" s="3" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="H110" s="5" t="n">
@@ -7460,7 +7460,7 @@
       </c>
       <c r="G111" s="3" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="H111" s="5" t="n">
@@ -7522,7 +7522,7 @@
       </c>
       <c r="G112" s="3" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="H112" s="5" t="n">
@@ -7584,7 +7584,7 @@
       </c>
       <c r="G113" s="3" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="H113" s="5" t="n">
@@ -7646,7 +7646,7 @@
       </c>
       <c r="G114" s="3" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="H114" s="5" t="n">
@@ -7708,7 +7708,7 @@
       </c>
       <c r="G115" s="3" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="H115" s="5" t="n">
@@ -7770,7 +7770,7 @@
       </c>
       <c r="G116" s="3" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="H116" s="5" t="n">
@@ -7832,7 +7832,7 @@
       </c>
       <c r="G117" s="3" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="H117" s="5" t="n">
@@ -7894,7 +7894,7 @@
       </c>
       <c r="G118" s="3" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="H118" s="5" t="n">
@@ -7956,7 +7956,7 @@
       </c>
       <c r="G119" s="3" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="H119" s="5" t="n">
@@ -8018,7 +8018,7 @@
       </c>
       <c r="G120" s="3" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="H120" s="5" t="n">
@@ -8080,7 +8080,7 @@
       </c>
       <c r="G121" s="3" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="H121" s="5" t="n">
@@ -8142,7 +8142,7 @@
       </c>
       <c r="G122" s="3" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="H122" s="5" t="n">
@@ -8204,7 +8204,7 @@
       </c>
       <c r="G123" s="3" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="H123" s="5" t="n">
@@ -8266,7 +8266,7 @@
       </c>
       <c r="G124" s="3" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="H124" s="5" t="n">
@@ -8475,7 +8475,7 @@
           <t>E | 343呎 (1房)
 $790万
 $23,038/呎
-(26年-06月-01日)</t>
+(26年-06月-02日)</t>
         </is>
       </c>
       <c r="G5" s="20" t="inlineStr">
@@ -8506,7 +8506,7 @@
           <t>B | 345呎 (1房)
 $802万
 $23,246/呎
-(26年-04月-23日)</t>
+(26年-04月-24日)</t>
         </is>
       </c>
       <c r="D6" s="20" t="inlineStr">
@@ -8530,7 +8530,7 @@
           <t>E | 343呎 (1房)
 $745万
 $21,720/呎
-(26年-04月-21日)</t>
+(26年-04月-22日)</t>
         </is>
       </c>
       <c r="G6" s="20" t="inlineStr">
@@ -8561,7 +8561,7 @@
           <t>B | 345呎 (1房)
 $795万
 $23,039/呎
-(26年-04月-21日)</t>
+(26年-04月-22日)</t>
         </is>
       </c>
       <c r="D7" s="20" t="inlineStr">
@@ -8577,7 +8577,7 @@
           <t>D | 339呎 (1房)
 $756万
 $22,299/呎
-(26年-07月-03日)</t>
+(26年-07月-27日)</t>
         </is>
       </c>
       <c r="F7" s="21" t="inlineStr">
@@ -8585,7 +8585,7 @@
           <t>E | 343呎 (1房)
 $738万
 $21,525/呎
-(26年-04月-21日)</t>
+(26年-04月-22日)</t>
         </is>
       </c>
       <c r="G7" s="21" t="inlineStr">
@@ -8593,7 +8593,7 @@
           <t>F | 345呎 (1房)
 $763万
 $22,111/呎
-(26年-04月-23日)</t>
+(26年-04月-24日)</t>
         </is>
       </c>
     </row>
@@ -8616,7 +8616,7 @@
           <t>B | 345呎 (1房)
 $788万
 $22,833/呎
-(26年-04月-23日)</t>
+(26年-04月-24日)</t>
         </is>
       </c>
       <c r="D8" s="21" t="inlineStr">
@@ -8624,7 +8624,7 @@
           <t>C | 338呎 (1房)
 $747万
 $22,099/呎
-(26年-05月-20日)</t>
+(26年-05月-21日)</t>
         </is>
       </c>
       <c r="E8" s="20" t="inlineStr">
@@ -8640,7 +8640,7 @@
           <t>E | 343呎 (1房)
 $732万
 $21,333/呎
-(26年-04月-21日)</t>
+(26年-04月-22日)</t>
         </is>
       </c>
       <c r="G8" s="21" t="inlineStr">
@@ -8648,7 +8648,7 @@
           <t>F | 345呎 (1房)
 $756万
 $21,917/呎
-(26年-04月-23日)</t>
+(26年-04月-24日)</t>
         </is>
       </c>
     </row>
@@ -8671,7 +8671,7 @@
           <t>B | 345呎 (1房)
 $781万
 $22,630/呎
-(26年-04月-23日)</t>
+(26年-04月-24日)</t>
         </is>
       </c>
       <c r="D9" s="21" t="inlineStr">
@@ -8679,7 +8679,7 @@
           <t>C | 338呎 (1房)
 $740万
 $21,904/呎
-(26年-04月-22日)</t>
+(26年-04月-23日)</t>
         </is>
       </c>
       <c r="E9" s="21" t="inlineStr">
@@ -8687,7 +8687,7 @@
           <t>D | 339呎 (1房)
 $743万
 $21,904/呎
-(26年-04月-23日)</t>
+(26年-04月-24日)</t>
         </is>
       </c>
       <c r="F9" s="21" t="inlineStr">
@@ -8695,7 +8695,7 @@
           <t>E | 343呎 (1房)
 $725万
 $21,144/呎
-(26年-04月-23日)</t>
+(26年-04月-24日)</t>
         </is>
       </c>
       <c r="G9" s="21" t="inlineStr">
@@ -8703,7 +8703,7 @@
           <t>F | 345呎 (1房)
 $749万
 $21,720/呎
-(26年-04月-22日)</t>
+(26年-04月-23日)</t>
         </is>
       </c>
     </row>
@@ -8726,7 +8726,7 @@
           <t>B | 345呎 (1房)
 $774万
 $22,430/呎
-(26年-04月-22日)</t>
+(26年-04月-23日)</t>
         </is>
       </c>
       <c r="D10" s="21" t="inlineStr">
@@ -8734,7 +8734,7 @@
           <t>C | 338呎 (1房)
 $734万
 $21,709/呎
-(26年-04月-23日)</t>
+(26年-04月-24日)</t>
         </is>
       </c>
       <c r="E10" s="21" t="inlineStr">
@@ -8742,7 +8742,7 @@
           <t>D | 339呎 (1房)
 $736万
 $21,709/呎
-(26年-04月-28日)</t>
+(26年-04月-29日)</t>
         </is>
       </c>
       <c r="F10" s="21" t="inlineStr">
@@ -8750,7 +8750,7 @@
           <t>E | 343呎 (1房)
 $719万
 $20,955/呎
-(26年-04月-26日)</t>
+(26年-04月-27日)</t>
         </is>
       </c>
       <c r="G10" s="21" t="inlineStr">
@@ -8758,7 +8758,7 @@
           <t>F | 345呎 (1房)
 $743万
 $21,526/呎
-(26年-04月-23日)</t>
+(26年-04月-24日)</t>
         </is>
       </c>
     </row>
@@ -8773,7 +8773,7 @@
           <t>A | 347呎 (1房)
 $789万
 $22,725/呎
-(26年-04月-23日)</t>
+(26年-04月-24日)</t>
         </is>
       </c>
       <c r="C11" s="21" t="inlineStr">
@@ -8781,7 +8781,7 @@
           <t>B | 345呎 (1房)
 $767万
 $22,230/呎
-(26年-04月-22日)</t>
+(26年-04月-23日)</t>
         </is>
       </c>
       <c r="D11" s="21" t="inlineStr">
@@ -8789,7 +8789,7 @@
           <t>C | 338呎 (1房)
 $727万
 $21,517/呎
-(26年-04月-23日)</t>
+(26年-04月-24日)</t>
         </is>
       </c>
       <c r="E11" s="21" t="inlineStr">
@@ -8797,7 +8797,7 @@
           <t>D | 339呎 (1房)
 $729万
 $21,515/呎
-(26年-04月-26日)</t>
+(26年-04月-27日)</t>
         </is>
       </c>
       <c r="F11" s="21" t="inlineStr">
@@ -8805,7 +8805,7 @@
           <t>E | 343呎 (1房)
 $712万
 $20,769/呎
-(26年-04月-22日)</t>
+(26年-04月-23日)</t>
         </is>
       </c>
       <c r="G11" s="21" t="inlineStr">
@@ -8813,7 +8813,7 @@
           <t>F | 345呎 (1房)
 $736万
 $21,334/呎
-(26年-04月-22日)</t>
+(26年-04月-23日)</t>
         </is>
       </c>
     </row>
@@ -8828,7 +8828,7 @@
           <t>A | 347呎 (1房)
 $779万
 $22,446/呎
-(26年-04月-22日)</t>
+(26年-04月-23日)</t>
         </is>
       </c>
       <c r="C12" s="21" t="inlineStr">
@@ -8836,7 +8836,7 @@
           <t>B | 345呎 (1房)
 $758万
 $21,959/呎
-(26年-04月-21日)</t>
+(26年-04月-22日)</t>
         </is>
       </c>
       <c r="D12" s="21" t="inlineStr">
@@ -8844,7 +8844,7 @@
           <t>C | 338呎 (1房)
 $721万
 $21,325/呎
-(26年-04月-21日)</t>
+(26年-04月-22日)</t>
         </is>
       </c>
       <c r="E12" s="21" t="inlineStr">
@@ -8852,7 +8852,7 @@
           <t>D | 339呎 (1房)
 $723万
 $21,323/呎
-(26年-04月-22日)</t>
+(26年-04月-23日)</t>
         </is>
       </c>
       <c r="F12" s="21" t="inlineStr">
@@ -8860,7 +8860,7 @@
           <t>E | 343呎 (1房)
 $706万
 $20,585/呎
-(26年-04月-22日)</t>
+(26年-04月-23日)</t>
         </is>
       </c>
       <c r="G12" s="21" t="inlineStr">
@@ -8868,7 +8868,7 @@
           <t>F | 345呎 (1房)
 $730万
 $21,146/呎
-(26年-04月-22日)</t>
+(26年-04月-23日)</t>
         </is>
       </c>
     </row>
@@ -8883,7 +8883,7 @@
           <t>A | 347呎 (1房)
 $768万
 $22,138/呎
-(26年-04月-23日)</t>
+(26年-04月-24日)</t>
         </is>
       </c>
       <c r="C13" s="21" t="inlineStr">
@@ -8891,7 +8891,7 @@
           <t>B | 345呎 (1房)
 $747万
 $21,654/呎
-(26年-04月-23日)</t>
+(26年-04月-24日)</t>
         </is>
       </c>
       <c r="D13" s="21" t="inlineStr">
@@ -8899,7 +8899,7 @@
           <t>C | 338呎 (1房)
 $714万
 $21,133/呎
-(26年-04月-22日)</t>
+(26年-04月-23日)</t>
         </is>
       </c>
       <c r="E13" s="21" t="inlineStr">
@@ -8907,7 +8907,7 @@
           <t>D | 339呎 (1房)
 $716万
 $21,135/呎
-(26年-04月-22日)</t>
+(26年-04月-23日)</t>
         </is>
       </c>
       <c r="F13" s="21" t="inlineStr">
@@ -8915,7 +8915,7 @@
           <t>E | 343呎 (1房)
 $700万
 $20,402/呎
-(26年-04月-23日)</t>
+(26年-04月-24日)</t>
         </is>
       </c>
       <c r="G13" s="21" t="inlineStr">
@@ -8923,7 +8923,7 @@
           <t>F | 345呎 (1房)
 $723万
 $20,958/呎
-(26年-04月-23日)</t>
+(26年-04月-24日)</t>
         </is>
       </c>
     </row>
@@ -8938,7 +8938,7 @@
           <t>A | 347呎 (1房)
 $762万
 $21,962/呎
-(26年-04月-21日)</t>
+(26年-04月-22日)</t>
         </is>
       </c>
       <c r="C14" s="21" t="inlineStr">
@@ -8946,7 +8946,7 @@
           <t>B | 345呎 (1房)
 $732万
 $21,219/呎
-(26年-04月-21日)</t>
+(26年-04月-22日)</t>
         </is>
       </c>
       <c r="D14" s="21" t="inlineStr">
@@ -8954,7 +8954,7 @@
           <t>C | 338呎 (1房)
 $701万
 $20,744/呎
-(26年-04月-23日)</t>
+(26年-04月-24日)</t>
         </is>
       </c>
       <c r="E14" s="21" t="inlineStr">
@@ -8962,7 +8962,7 @@
           <t>D | 339呎 (1房)
 $703万
 $20,743/呎
-(26年-04月-23日)</t>
+(26年-04月-24日)</t>
         </is>
       </c>
       <c r="F14" s="21" t="inlineStr">
@@ -8970,7 +8970,7 @@
           <t>E | 343呎 (1房)
 $687万
 $20,022/呎
-(26年-04月-23日)</t>
+(26年-04月-24日)</t>
         </is>
       </c>
       <c r="G14" s="21" t="inlineStr">
@@ -8978,7 +8978,7 @@
           <t>F | 345呎 (1房)
 $710万
 $20,569/呎
-(26年-04月-23日)</t>
+(26年-04月-24日)</t>
         </is>
       </c>
     </row>
@@ -8993,7 +8993,7 @@
           <t>A | 347呎 (1房)
 $739万
 $21,286/呎
-(26年-04月-26日)</t>
+(26年-04月-27日)</t>
         </is>
       </c>
       <c r="C15" s="21" t="inlineStr">
@@ -9001,7 +9001,7 @@
           <t>B | 345呎 (1房)
 $718万
 $20,824/呎
-(26年-04月-26日)</t>
+(26年-04月-27日)</t>
         </is>
       </c>
       <c r="D15" s="21" t="inlineStr">
@@ -9009,7 +9009,7 @@
           <t>C | 338呎 (1房)
 $688万
 $20,355/呎
-(26年-04月-21日)</t>
+(26年-04月-22日)</t>
         </is>
       </c>
       <c r="E15" s="21" t="inlineStr">
@@ -9017,7 +9017,7 @@
           <t>D | 339呎 (1房)
 $690万
 $20,358/呎
-(26年-04月-21日)</t>
+(26年-04月-22日)</t>
         </is>
       </c>
       <c r="F15" s="21" t="inlineStr">
@@ -9025,7 +9025,7 @@
           <t>E | 343呎 (1房)
 $674万
 $19,650/呎
-(26年-04月-22日)</t>
+(26年-04月-23日)</t>
         </is>
       </c>
       <c r="G15" s="21" t="inlineStr">
@@ -9033,7 +9033,7 @@
           <t>F | 345呎 (1房)
 $696万
 $20,186/呎
-(26年-04月-22日)</t>
+(26年-04月-23日)</t>
         </is>
       </c>
     </row>
@@ -9048,7 +9048,7 @@
           <t>A | 347呎 (1房)
 $716万
 $20,648/呎
-(26年-04月-23日)</t>
+(26年-04月-24日)</t>
         </is>
       </c>
       <c r="C16" s="21" t="inlineStr">
@@ -9056,7 +9056,7 @@
           <t>B | 345呎 (1房)
 $695万
 $20,134/呎
-(26年-04月-23日)</t>
+(26年-04月-24日)</t>
         </is>
       </c>
       <c r="D16" s="21" t="inlineStr">
@@ -9064,7 +9064,7 @@
           <t>C | 338呎 (1房)
 $671万
 $19,843/呎
-(26年-04月-23日)</t>
+(26年-04月-24日)</t>
         </is>
       </c>
       <c r="E16" s="21" t="inlineStr">
@@ -9072,7 +9072,7 @@
           <t>D | 339呎 (1房)
 $673万
 $19,844/呎
-(26年-04月-23日)</t>
+(26年-04月-24日)</t>
         </is>
       </c>
       <c r="F16" s="21" t="inlineStr">
@@ -9080,7 +9080,7 @@
           <t>E | 343呎 (1房)
 $657万
 $19,155/呎
-(26年-04月-23日)</t>
+(26年-04月-24日)</t>
         </is>
       </c>
       <c r="G16" s="21" t="inlineStr">
@@ -9088,7 +9088,7 @@
           <t>F | 345呎 (1房)
 $681万
 $19,742/呎
-(26年-04月-23日)</t>
+(26年-04月-24日)</t>
         </is>
       </c>
     </row>
@@ -9103,7 +9103,7 @@
           <t>A | 347呎 (1房)
 $698万
 $20,113/呎
-(26年-04月-28日)</t>
+(26年-04月-29日)</t>
         </is>
       </c>
       <c r="C17" s="21" t="inlineStr">
@@ -9111,7 +9111,7 @@
           <t>B | 345呎 (1房)
 $673万
 $19,513/呎
-(26年-04月-21日)</t>
+(26年-04月-22日)</t>
         </is>
       </c>
       <c r="D17" s="21" t="inlineStr">
@@ -9119,7 +9119,7 @@
           <t>C | 338呎 (1房)
 $658万
 $19,473/呎
-(26年-04月-22日)</t>
+(26年-04月-23日)</t>
         </is>
       </c>
       <c r="E17" s="21" t="inlineStr">
@@ -9127,7 +9127,7 @@
           <t>D | 339呎 (1房)
 $660万
 $19,472/呎
-(26年-04月-23日)</t>
+(26年-04月-24日)</t>
         </is>
       </c>
       <c r="F17" s="21" t="inlineStr">
@@ -9135,7 +9135,7 @@
           <t>E | 343呎 (1房)
 $645万
 $18,796/呎
-(26年-04月-22日)</t>
+(26年-04月-23日)</t>
         </is>
       </c>
       <c r="G17" s="21" t="inlineStr">
@@ -9143,7 +9143,7 @@
           <t>F | 345呎 (1房)
 $672万
 $19,470/呎
-(26年-04月-23日)</t>
+(26年-04月-24日)</t>
         </is>
       </c>
     </row>
@@ -9158,7 +9158,7 @@
           <t>A | 347呎 (1房)
 $695万
 $20,017/呎
-(26年-04月-23日)</t>
+(26年-04月-24日)</t>
         </is>
       </c>
       <c r="C18" s="21" t="inlineStr">
@@ -9166,7 +9166,7 @@
           <t>B | 345呎 (1房)
 $669万
 $19,389/呎
-(26年-04月-23日)</t>
+(26年-04月-24日)</t>
         </is>
       </c>
       <c r="D18" s="21" t="inlineStr">
@@ -9174,7 +9174,7 @@
           <t>C | 338呎 (1房)
 $657万
 $19,426/呎
-(26年-04月-23日)</t>
+(26年-04月-24日)</t>
         </is>
       </c>
       <c r="E18" s="21" t="inlineStr">
@@ -9182,7 +9182,7 @@
           <t>D | 339呎 (1房)
 $659万
 $19,428/呎
-(26年-04月-23日)</t>
+(26年-04月-24日)</t>
         </is>
       </c>
       <c r="F18" s="21" t="inlineStr">
@@ -9190,7 +9190,7 @@
           <t>E | 343呎 (1房)
 $643万
 $18,755/呎
-(26年-04月-22日)</t>
+(26年-04月-23日)</t>
         </is>
       </c>
       <c r="G18" s="21" t="inlineStr">
@@ -9198,7 +9198,7 @@
           <t>F | 345呎 (1房)
 $671万
 $19,457/呎
-(26年-04月-21日)</t>
+(26年-04月-22日)</t>
         </is>
       </c>
     </row>
@@ -9213,7 +9213,7 @@
           <t>A | 347呎 (1房)
 $682万
 $19,640/呎
-(26年-04月-23日)</t>
+(26年-04月-24日)</t>
         </is>
       </c>
       <c r="C19" s="21" t="inlineStr">
@@ -9221,7 +9221,7 @@
           <t>B | 345呎 (1房)
 $656万
 $19,026/呎
-(26年-04月-21日)</t>
+(26年-04月-22日)</t>
         </is>
       </c>
       <c r="D19" s="21" t="inlineStr">
@@ -9229,7 +9229,7 @@
           <t>C | 338呎 (1房)
 $644万
 $19,065/呎
-(26年-04月-22日)</t>
+(26年-04月-23日)</t>
         </is>
       </c>
       <c r="E19" s="21" t="inlineStr">
@@ -9237,7 +9237,7 @@
           <t>D | 339呎 (1房)
 $646万
 $19,065/呎
-(26年-04月-22日)</t>
+(26年-04月-23日)</t>
         </is>
       </c>
       <c r="F19" s="21" t="inlineStr">
@@ -9245,7 +9245,7 @@
           <t>E | 343呎 (1房)
 $631万
 $18,402/呎
-(26年-04月-22日)</t>
+(26年-04月-23日)</t>
         </is>
       </c>
       <c r="G19" s="21" t="inlineStr">
@@ -9253,7 +9253,7 @@
           <t>F | 345呎 (1房)
 $659万
 $19,093/呎
-(26年-04月-22日)</t>
+(26年-04月-23日)</t>
         </is>
       </c>
     </row>
@@ -9268,7 +9268,7 @@
           <t>A | 347呎 (1房)
 $676万
 $19,467/呎
-(26年-04月-22日)</t>
+(26年-04月-23日)</t>
         </is>
       </c>
       <c r="C20" s="21" t="inlineStr">
@@ -9276,7 +9276,7 @@
           <t>B | 345呎 (1房)
 $650万
 $18,855/呎
-(26年-04月-22日)</t>
+(26年-04月-23日)</t>
         </is>
       </c>
       <c r="D20" s="21" t="inlineStr">
@@ -9284,7 +9284,7 @@
           <t>C | 338呎 (1房)
 $639万
 $18,893/呎
-(26年-04月-21日)</t>
+(26年-04月-22日)</t>
         </is>
       </c>
       <c r="E20" s="21" t="inlineStr">
@@ -9292,7 +9292,7 @@
           <t>D | 339呎 (1房)
 $640万
 $18,894/呎
-(26年-04月-23日)</t>
+(26年-04月-24日)</t>
         </is>
       </c>
       <c r="F20" s="21" t="inlineStr">
@@ -9300,7 +9300,7 @@
           <t>E | 343呎 (1房)
 $626万
 $18,239/呎
-(26年-04月-21日)</t>
+(26年-04月-22日)</t>
         </is>
       </c>
       <c r="G20" s="21" t="inlineStr">
@@ -9308,7 +9308,7 @@
           <t>F | 345呎 (1房)
 $653万
 $18,922/呎
-(26年-04月-22日)</t>
+(26年-04月-23日)</t>
         </is>
       </c>
     </row>
@@ -9323,7 +9323,7 @@
           <t>A | 347呎 (1房)
 $670万
 $19,294/呎
-(26年-04月-22日)</t>
+(26年-04月-23日)</t>
         </is>
       </c>
       <c r="C21" s="21" t="inlineStr">
@@ -9331,7 +9331,7 @@
           <t>B | 345呎 (1房)
 $645万
 $18,687/呎
-(26年-04月-23日)</t>
+(26年-04月-24日)</t>
         </is>
       </c>
       <c r="D21" s="21" t="inlineStr">
@@ -9339,7 +9339,7 @@
           <t>C | 338呎 (1房)
 $633万
 $18,725/呎
-(26年-04月-22日)</t>
+(26年-04月-23日)</t>
         </is>
       </c>
       <c r="E21" s="21" t="inlineStr">
@@ -9347,7 +9347,7 @@
           <t>D | 339呎 (1房)
 $635万
 $18,726/呎
-(26年-04月-22日)</t>
+(26年-04月-23日)</t>
         </is>
       </c>
       <c r="F21" s="21" t="inlineStr">
@@ -9355,7 +9355,7 @@
           <t>E | 343呎 (1房)
 $620万
 $18,076/呎
-(26年-04月-22日)</t>
+(26年-04月-23日)</t>
         </is>
       </c>
       <c r="G21" s="21" t="inlineStr">
@@ -9363,7 +9363,7 @@
           <t>F | 345呎 (1房)
 $647万
 $18,754/呎
-(26年-04月-22日)</t>
+(26年-04月-23日)</t>
         </is>
       </c>
     </row>
@@ -9378,7 +9378,7 @@
           <t>A | 347呎 (1房)
 $664万
 $19,121/呎
-(26年-04月-23日)</t>
+(26年-04月-24日)</t>
         </is>
       </c>
       <c r="C22" s="21" t="inlineStr">
@@ -9386,7 +9386,7 @@
           <t>B | 345呎 (1房)
 $639万
 $18,522/呎
-(26年-04月-22日)</t>
+(26年-04月-23日)</t>
         </is>
       </c>
       <c r="D22" s="21" t="inlineStr">
@@ -9394,7 +9394,7 @@
           <t>C | 338呎 (1房)
 $627万
 $18,559/呎
-(26年-04月-22日)</t>
+(26年-04月-23日)</t>
         </is>
       </c>
       <c r="E22" s="21" t="inlineStr">
@@ -9402,7 +9402,7 @@
           <t>D | 339呎 (1房)
 $629万
 $18,560/呎
-(26年-04月-22日)</t>
+(26年-04月-23日)</t>
         </is>
       </c>
       <c r="F22" s="21" t="inlineStr">
@@ -9410,7 +9410,7 @@
           <t>E | 343呎 (1房)
 $615万
 $17,916/呎
-(26年-04月-23日)</t>
+(26年-04月-24日)</t>
         </is>
       </c>
       <c r="G22" s="21" t="inlineStr">
@@ -9418,7 +9418,7 @@
           <t>F | 345呎 (1房)
 $641万
 $18,588/呎
-(26年-04月-22日)</t>
+(26年-04月-23日)</t>
         </is>
       </c>
     </row>
@@ -9433,7 +9433,7 @@
           <t>A | 347呎 (1房)
 $652万
 $18,784/呎
-(26年-04月-23日)</t>
+(26年-04月-24日)</t>
         </is>
       </c>
       <c r="C23" s="21" t="inlineStr">
@@ -9441,7 +9441,7 @@
           <t>B | 345呎 (1房)
 $628万
 $18,194/呎
-(26年-04月-23日)</t>
+(26年-04月-24日)</t>
         </is>
       </c>
       <c r="D23" s="21" t="inlineStr">
@@ -9449,7 +9449,7 @@
           <t>C | 338呎 (1房)
 $616万
 $18,231/呎
-(26年-04月-21日)</t>
+(26年-04月-22日)</t>
         </is>
       </c>
       <c r="E23" s="21" t="inlineStr">
@@ -9457,7 +9457,7 @@
           <t>D | 339呎 (1房)
 $618万
 $18,233/呎
-(26年-04月-21日)</t>
+(26年-04月-22日)</t>
         </is>
       </c>
       <c r="F23" s="21" t="inlineStr">
@@ -9465,7 +9465,7 @@
           <t>E | 343呎 (1房)
 $602万
 $17,554/呎
-(26年-04月-21日)</t>
+(26年-04月-22日)</t>
         </is>
       </c>
       <c r="G23" s="21" t="inlineStr">
@@ -9473,7 +9473,7 @@
           <t>F | 345呎 (1房)
 $630万
 $18,258/呎
-(26年-04月-21日)</t>
+(26年-04月-22日)</t>
         </is>
       </c>
     </row>
@@ -9490,7 +9490,7 @@
           <t>C | 343呎 (1房)
 $600万
 $17,487/呎
-(26年-04月-22日)</t>
+(26年-04月-23日)</t>
         </is>
       </c>
       <c r="E24" s="21" t="inlineStr">
@@ -9498,7 +9498,7 @@
           <t>D | 339呎 (1房)
 $602万
 $17,752/呎
-(26年-04月-22日)</t>
+(26年-04月-23日)</t>
         </is>
       </c>
       <c r="F24" s="21" t="inlineStr">
@@ -9506,7 +9506,7 @@
           <t>E | 343呎 (1房)
 $579万
 $16,880/呎
-(26年-04月-22日)</t>
+(26年-04月-23日)</t>
         </is>
       </c>
       <c r="G24" s="21" t="inlineStr">
@@ -9514,7 +9514,7 @@
           <t>F | 345呎 (1房)
 $613万
 $17,780/呎
-(26年-04月-22日)</t>
+(26年-04月-23日)</t>
         </is>
       </c>
     </row>
@@ -9531,7 +9531,7 @@
           <t>C | 305呎 (1房)
 $656万
 $21,525/呎
-(26年-04月-22日)</t>
+(26年-04月-23日)</t>
         </is>
       </c>
       <c r="E25" s="21" t="inlineStr">
@@ -9539,7 +9539,7 @@
           <t>D | 301呎 (1房)
 $664万
 $22,076/呎
-(26年-04月-22日)</t>
+(26年-04月-23日)</t>
         </is>
       </c>
       <c r="F25" s="21" t="inlineStr">
@@ -9547,7 +9547,7 @@
           <t>E | 343呎 (1房)
 $586万
 $17,087/呎
-(26年-04月-22日)</t>
+(26年-04月-23日)</t>
         </is>
       </c>
       <c r="G25" s="21" t="inlineStr">
@@ -9555,7 +9555,7 @@
           <t>F | 345呎 (1房)
 $618万
 $17,904/呎
-(26年-04月-22日)</t>
+(26年-04月-23日)</t>
         </is>
       </c>
     </row>
